--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlGlobal.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlGlobal.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="BrawlGlobal" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -20,43 +20,85 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t xml:space="preserve">##var#column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">##type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">##group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">##desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CellSize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>##var#column</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>##desc</t>
+  </si>
+  <si>
+    <t>CellSize</t>
+  </si>
+  <si>
+    <t>int</t>
   </si>
   <si>
     <r>
       <rPr>
+        <rFont val="Noto Sans SC"/>
+        <charset val="1"/>
+        <family val="2"/>
         <sz val="11"/>
-        <rFont val="Noto Sans SC"/>
-        <family val="2"/>
       </rPr>
-      <t xml:space="preserve">格子尺寸（米），必须大于</t>
+      <t>格子尺寸（米），必须大于</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Arial"/>
+        <charset val="1"/>
         <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0</t>
+      <t>0</t>
     </r>
+  </si>
+  <si>
+    <t>MaxLevel</t>
+  </si>
+  <si>
+    <t>最高等级（英雄和单位）</t>
+  </si>
+  <si>
+    <t>HeroSpawnProtectionDuration</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">英雄出生完成后的无敌时间 </t>
+  </si>
+  <si>
+    <t>HeroSpawnDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">英雄出生阶段时间 </t>
+  </si>
+  <si>
+    <t>HeroDeathDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">英雄死亡保留时间 </t>
+  </si>
+  <si>
+    <t>RedRespawnPointNpcId</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>红方复活点NPC配置ID</t>
+  </si>
+  <si>
+    <t>BlueRespawnPointNpcId</t>
+  </si>
+  <si>
+    <t>蓝方复活点NPC配置ID</t>
   </si>
 </sst>
 </file>
@@ -64,24 +106,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
+    <numFmt numFmtId="0" formatCode="General"/>
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -95,7 +128,13 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -105,15 +144,10 @@
       <sz val="11"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -126,15 +160,9 @@
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border diagonalUp="1" diagonalDown="1">
       <left/>
       <right/>
       <top/>
@@ -142,65 +170,33 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="21">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellStyleXfs count="7">
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="6">
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
+    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Normal" xfId="20"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+    <cellStyle name="Normal" xfId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -222,7 +218,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -435,46 +431,137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col min="1" max="3" width="20" customWidth="1" style="1"/>
+    <col min="4" max="4" width="38" customWidth="1" style="1"/>
+    <col min="5" max="5" width="12" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E1"/>
+    </row>
+    <row r="2" ht="25" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="0">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="15">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="15">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="15">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="15">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" ht="15">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="8" ht="15">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2002</v>
       </c>
     </row>
   </sheetData>
@@ -486,4 +573,9 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlGlobal.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlGlobal.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="BrawlGlobal" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -20,101 +20,141 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>##var#column</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>##desc</t>
-  </si>
-  <si>
-    <t>CellSize</t>
-  </si>
-  <si>
-    <t>int</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
+  <si>
+    <t xml:space="preserve">##var#column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CellSize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
   </si>
   <si>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="Noto Sans SC"/>
+        <family val="2"/>
         <charset val="1"/>
-        <family val="2"/>
-        <sz val="11"/>
       </rPr>
-      <t>格子尺寸（米），必须大于</t>
+      <t xml:space="preserve">格子尺寸（米），必须大于</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
-        <sz val="11"/>
       </rPr>
-      <t>0</t>
+      <t xml:space="preserve">0</t>
     </r>
   </si>
   <si>
-    <t>MaxLevel</t>
-  </si>
-  <si>
-    <t>最高等级（英雄和单位）</t>
-  </si>
-  <si>
-    <t>HeroSpawnProtectionDuration</t>
-  </si>
-  <si>
-    <t>float</t>
+    <t xml:space="preserve">MaxLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最高等级（英雄和单位）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeroSpawnProtectionDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">float</t>
   </si>
   <si>
     <t xml:space="preserve">英雄出生完成后的无敌时间 </t>
   </si>
   <si>
-    <t>HeroSpawnDuration</t>
+    <t xml:space="preserve">HeroSpawnDuration</t>
   </si>
   <si>
     <t xml:space="preserve">英雄出生阶段时间 </t>
   </si>
   <si>
-    <t>HeroDeathDuration</t>
+    <t xml:space="preserve">HeroDeathDuration</t>
   </si>
   <si>
     <t xml:space="preserve">英雄死亡保留时间 </t>
   </si>
   <si>
-    <t>RedRespawnPointNpcId</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>红方复活点NPC配置ID</t>
-  </si>
-  <si>
-    <t>BlueRespawnPointNpcId</t>
-  </si>
-  <si>
-    <t>蓝方复活点NPC配置ID</t>
+    <t xml:space="preserve">RedRespawnPointNpcId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">红方复活点NPC配置ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlueRespawnPointNpcId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蓝方复活点NPC配置ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CameraDistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通用战斗相机到观察点的直线距离（米），大于0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CameraPitch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通用战斗相机X轴俯角（度），大于0且小于90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CameraYaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">通用战斗相机Y轴水平角（度），0朝世界正Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CameraFieldOfView</t>
+  </si>
+  <si>
+    <t xml:space="preserve">透视相机垂直FOV（度），大于0且小于179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CameraTargetHeight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">观察点相对主角原点的世界Y偏移（米）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -128,7 +168,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -162,7 +202,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="1" diagonalDown="1">
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -170,33 +210,73 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+  <cellXfs count="7">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
-    <cellStyle name="Normal" xfId="6"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal" xfId="20"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -431,19 +511,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1" style="1"/>
-    <col min="4" max="4" width="38" customWidth="1" style="1"/>
-    <col min="5" max="5" width="12" customWidth="1" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
+    <row r="1" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -456,9 +536,8 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1"/>
-    </row>
-    <row r="2" ht="25" customHeight="1">
+    </row>
+    <row r="2" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -469,11 +548,11 @@
       <c r="D2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -484,11 +563,11 @@
       <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="0">
+      <c r="E3" s="5" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="15">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -498,70 +577,149 @@
       <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="0">
+      <c r="E4" s="5" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="15">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="0">
+      <c r="E5" s="5" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="15">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="0">
+      <c r="E6" s="5" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="7" ht="15">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="n">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="8" ht="15">
-      <c r="A8" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="D8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="1">
-        <v>2002</v>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -573,9 +731,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlGlobal.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlGlobal.xlsx
@@ -651,7 +651,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
